--- a/api/clv2/xlsx/en/EarmarkingCategory.xlsx
+++ b/api/clv2/xlsx/en/EarmarkingCategory.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="17">
   <si>
     <t>code</t>
   </si>
@@ -23,12 +23,6 @@
   </si>
   <si>
     <t>description</t>
-  </si>
-  <si>
-    <t>category</t>
-  </si>
-  <si>
-    <t>url</t>
   </si>
   <si>
     <t>status</t>
@@ -402,10 +396,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -418,67 +412,61 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="B2" t="s">
         <v>5</v>
       </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="2" spans="1:6">
-      <c r="A2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" t="s">
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
         <v>7</v>
       </c>
-      <c r="C2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>9</v>
-      </c>
     </row>
-    <row r="3" spans="1:6">
-      <c r="A3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" t="s">
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
         <v>11</v>
       </c>
-      <c r="C3" t="s">
+      <c r="B4" t="s">
         <v>12</v>
       </c>
-      <c r="F3" t="s">
-        <v>9</v>
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" t="s">
+        <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
-      <c r="A4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" t="s">
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
         <v>14</v>
       </c>
-      <c r="C4" t="s">
+      <c r="B5" t="s">
         <v>15</v>
       </c>
-      <c r="F4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" t="s">
+      <c r="C5" t="s">
         <v>16</v>
       </c>
-      <c r="B5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" t="s">
-        <v>18</v>
-      </c>
-      <c r="F5" t="s">
-        <v>9</v>
+      <c r="D5" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
